--- a/Black_Ex3A_tables.xlsx
+++ b/Black_Ex3A_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\disco\Documents\DATA_Labs\W2_Workshop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2D7A522-C27E-4667-8EE0-257612035290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11634102-4A0F-4AA1-963F-66B202103FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="3" xr2:uid="{13A74D8E-5303-49EC-AE92-098F413C024B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{13A74D8E-5303-49EC-AE92-098F413C024B}"/>
   </bookViews>
   <sheets>
     <sheet name="Client" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="56">
   <si>
     <t>Client</t>
   </si>
@@ -151,13 +151,70 @@
   </si>
   <si>
     <t>Payment Confirmation</t>
+  </si>
+  <si>
+    <t>Zipcode</t>
+  </si>
+  <si>
+    <t>Judy Tobin</t>
+  </si>
+  <si>
+    <t>(608) 241-823</t>
+  </si>
+  <si>
+    <t>theartistsjudy@realartists.com</t>
+  </si>
+  <si>
+    <t>8750 Bear Run Way</t>
+  </si>
+  <si>
+    <t>Anchorage</t>
+  </si>
+  <si>
+    <t>Alaska</t>
+  </si>
+  <si>
+    <t>A1D</t>
+  </si>
+  <si>
+    <t>DOG-001</t>
+  </si>
+  <si>
+    <t>Picasso</t>
+  </si>
+  <si>
+    <t>Husky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Likes to run off, stops walking if tired and flops to ground, and barely listens. </t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>WP2I72</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Bridgewater Park</t>
+  </si>
+  <si>
+    <t>2 miles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This was a much more fun route for Picasso and he enjoyed the scenery as well. </t>
+  </si>
+  <si>
+    <t>Debit Card</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -169,6 +226,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -191,17 +256,82 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="73">
+  <dxfs count="26">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -212,6 +342,90 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.749961851863155"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.749961851863155"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="7" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -226,492 +440,15 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="4" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.749961851863155"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.749961851863155"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.749961851863155"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -737,7 +474,39 @@
 </table>
 </file>
 
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{F93B6BCD-7DB8-4B8A-8CBB-86BE3FC8866C}" name="Table12" displayName="Table12" ref="E1:J2" totalsRowShown="0">
+  <autoFilter ref="E1:J2" xr:uid="{F93B6BCD-7DB8-4B8A-8CBB-86BE3FC8866C}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{520C9A08-423E-4348-9056-3977722318FD}" name="Payment ID"/>
+    <tableColumn id="2" xr3:uid="{14DE9BBD-5296-4B25-B5D0-156202824B2F}" name="Payment Date" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{E9CC7BAA-6B04-4283-9DF3-D582BB8E3A2E}" name="Payment Method"/>
+    <tableColumn id="4" xr3:uid="{CA70E976-FBCC-4691-9561-B998B46D97DD}" name="Price"/>
+    <tableColumn id="5" xr3:uid="{6BA95B7C-E39C-43DC-95EC-F03EEB2F6D14}" name="Payment Confirmation"/>
+    <tableColumn id="7" xr3:uid="{07145FF9-A6FF-4215-825E-52D08B438C14}" name="Appointment ID"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{056FE10F-534A-46AD-905C-9CEF2499997C}" name="Table7" displayName="Table7" ref="E1:L16" totalsRowShown="0">
+  <autoFilter ref="E1:L16" xr:uid="{056FE10F-534A-46AD-905C-9CEF2499997C}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{FEA18169-7067-4E70-A3FC-468C7F2647EC}" name="Client ID"/>
+    <tableColumn id="2" xr3:uid="{B001B265-9C92-4294-BF24-576B0891677B}" name="Client"/>
+    <tableColumn id="3" xr3:uid="{7A87D583-2F08-4D9A-B9C1-AE9D8646B6BC}" name="Phone Number"/>
+    <tableColumn id="4" xr3:uid="{1BAF5890-504D-4FC2-8956-736C91E2F40E}" name="Email"/>
+    <tableColumn id="5" xr3:uid="{5315ECE8-11FC-4E4E-869F-09F2044789EF}" name="Street"/>
+    <tableColumn id="6" xr3:uid="{96A239B8-B7A8-4EED-8251-90307F188278}" name="City"/>
+    <tableColumn id="7" xr3:uid="{F1B87B8D-5EF8-4B3F-ABC7-3822857C27DF}" name="State"/>
+    <tableColumn id="8" xr3:uid="{23DAB8C0-AD2C-4D50-A1C1-E3EC136254C9}" name="Zipcode"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F5ABC271-3232-4CAF-958B-82B403E5038B}" name="Table3" displayName="Table3" ref="A1:B8" totalsRowShown="0">
   <autoFilter ref="A1:B8" xr:uid="{F5ABC271-3232-4CAF-958B-82B403E5038B}"/>
   <tableColumns count="2">
@@ -748,7 +517,23 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{F5762837-5039-4153-835B-A3A9411286EA}" name="Table8" displayName="Table8" ref="F1:L11" totalsRowShown="0">
+  <autoFilter ref="F1:L11" xr:uid="{F5762837-5039-4153-835B-A3A9411286EA}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{4B8D7DD2-9A60-4399-852C-18E9395B17E8}" name="Dog ID"/>
+    <tableColumn id="2" xr3:uid="{F5139BC5-5CF9-43B4-982A-B9720B611123}" name="Dog Tag"/>
+    <tableColumn id="3" xr3:uid="{D37F154A-769B-4728-8D87-F4921B940EC9}" name="Dog Name"/>
+    <tableColumn id="4" xr3:uid="{EA47AE1E-9511-4F1D-91A5-A59E251092F8}" name="Breed"/>
+    <tableColumn id="5" xr3:uid="{C7B76D1E-56EF-4360-8E07-A606D26AC27A}" name="Date of Birth"/>
+    <tableColumn id="6" xr3:uid="{48DCBADF-852B-4AA0-A1F0-AE019AEB21CE}" name="Dog Notes"/>
+    <tableColumn id="7" xr3:uid="{3CAB48A2-DB02-4944-9E80-AAADD72CE91E}" name="Client ID"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F1BED0AE-73C6-49A2-96F4-B4169F0FAF91}" name="Table4" displayName="Table4" ref="A1:B7" totalsRowShown="0">
   <autoFilter ref="A1:B7" xr:uid="{F1BED0AE-73C6-49A2-96F4-B4169F0FAF91}"/>
   <tableColumns count="2">
@@ -759,7 +544,23 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{24144159-EFD9-4047-AC4E-947930A02EC7}" name="Table10" displayName="Table10" ref="D1:J10" totalsRowShown="0">
+  <autoFilter ref="D1:J10" xr:uid="{24144159-EFD9-4047-AC4E-947930A02EC7}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{53E4CFAA-57AA-4FF3-BFEB-594530D0FE90}" name="Appointment ID"/>
+    <tableColumn id="2" xr3:uid="{01B7D370-EDB6-48EF-A5E6-37181DC3FAA1}" name="Date"/>
+    <tableColumn id="3" xr3:uid="{0E05CBCE-11EE-4AD1-B747-85AEBD0F6C66}" name="Time"/>
+    <tableColumn id="4" xr3:uid="{51138DC9-D70E-4CBB-B20D-9FAA75A8B6C0}" name="Duration"/>
+    <tableColumn id="5" xr3:uid="{915C52D7-C0CE-47BF-9CBB-19593F070FD4}" name="Status"/>
+    <tableColumn id="6" xr3:uid="{139B6D15-AB1F-4188-AD3C-B6D1A1B2A23E}" name="Client ID"/>
+    <tableColumn id="7" xr3:uid="{2EC7245C-15A4-4EB8-9FB0-415F577BD1F3}" name="Column1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0BDFA9AB-8789-4B44-B33E-0BECBAC2B861}" name="Table5" displayName="Table5" ref="A1:B8" totalsRowShown="0">
   <autoFilter ref="A1:B8" xr:uid="{0BDFA9AB-8789-4B44-B33E-0BECBAC2B861}"/>
   <tableColumns count="2">
@@ -770,9 +571,25 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{237DE74A-EA93-48D0-975A-89765B17117B}" name="Table9" displayName="Table9" ref="A1:B8" totalsRowShown="0" headerRowCellStyle="Normal" dataCellStyle="Normal">
-  <autoFilter ref="A1:B8" xr:uid="{237DE74A-EA93-48D0-975A-89765B17117B}"/>
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F557B896-1864-4D39-B1EA-A249ADF1541B}" name="Table11" displayName="Table11" ref="D1:J2" totalsRowShown="0">
+  <autoFilter ref="D1:J2" xr:uid="{F557B896-1864-4D39-B1EA-A249ADF1541B}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{440A8058-19EA-43E0-B1E9-9D13853D0A5D}" name="Log ID"/>
+    <tableColumn id="2" xr3:uid="{C17DBF11-6F98-4162-9D34-3679B607F5D9}" name="Notes" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{DEB41138-BE17-4091-A461-CF70D7BE9AF1}" name="Walking Route"/>
+    <tableColumn id="4" xr3:uid="{3F6A3B3A-27A8-4F3A-9A57-444CEE0E8570}" name="Distance"/>
+    <tableColumn id="5" xr3:uid="{8C5D4724-85D4-4F91-9BAD-3F29FE630F4E}" name="City"/>
+    <tableColumn id="6" xr3:uid="{F701AB5D-670B-4A05-85DD-9FDECC1E94E8}" name="Appointment ID"/>
+    <tableColumn id="7" xr3:uid="{72424326-6BA4-4EC5-908F-205855ADE502}" name="Dog ID"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{237DE74A-EA93-48D0-975A-89765B17117B}" name="Table9" displayName="Table9" ref="A1:B7" totalsRowShown="0" headerRowCellStyle="Normal" dataCellStyle="Normal">
+  <autoFilter ref="A1:B7" xr:uid="{237DE74A-EA93-48D0-975A-89765B17117B}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{9260D494-27B5-4262-B637-15926535BAE6}" name="Payments" dataCellStyle="Normal"/>
     <tableColumn id="2" xr3:uid="{7271ABDD-2288-44A9-976B-1B9A60FD26DD}" name="Keys" dataCellStyle="Normal"/>
@@ -1098,60 +915,117 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E713B4D7-C1B2-4E5C-A3EF-9243C1ABFC58}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.453125" customWidth="1"/>
     <col min="2" max="2" width="27.453125" customWidth="1"/>
+    <col min="4" max="4" width="12.26953125" customWidth="1"/>
+    <col min="5" max="5" width="13.36328125" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" customWidth="1"/>
+    <col min="7" max="7" width="18.54296875" customWidth="1"/>
+    <col min="8" max="8" width="29.36328125" customWidth="1"/>
+    <col min="9" max="9" width="19.26953125" customWidth="1"/>
+    <col min="10" max="10" width="13.08984375" customWidth="1"/>
+    <col min="11" max="11" width="10.54296875" customWidth="1"/>
+    <col min="12" max="12" width="15.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2">
+        <v>99501</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1160,84 +1034,136 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2">
+    <cfRule type="containsText" dxfId="23" priority="1" operator="containsText" text="Client ID">
+      <formula>NOT(ISERROR(SEARCH("Client ID",A2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9">
+    <cfRule type="containsText" dxfId="22" priority="3" operator="containsText" text="ZipCode">
+      <formula>NOT(ISERROR(SEARCH("ZipCode",A9)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2">
+    <cfRule type="containsText" dxfId="21" priority="2" operator="containsText" text="PK">
+      <formula>NOT(ISERROR(SEARCH("PK",B2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="containsText" dxfId="6" priority="4" operator="containsText" text="FK">
+    <cfRule type="containsText" dxfId="20" priority="4" operator="containsText" text="FK">
       <formula>NOT(ISERROR(SEARCH("FK",B9)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A9">
-    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="ZipCode">
-      <formula>NOT(ISERROR(SEARCH("ZipCode",A9)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2">
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="PK">
-      <formula>NOT(ISERROR(SEARCH("PK",B2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Client ID">
-      <formula>NOT(ISERROR(SEARCH("Client ID",A2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{B3AB6D80-3956-4FDC-9F59-E7C63866671B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
+  <tableParts count="2">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E78AA8F-C1B4-4B6C-BCB4-4282F696A9E2}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.26953125" customWidth="1"/>
     <col min="2" max="2" width="17.7265625" customWidth="1"/>
+    <col min="7" max="7" width="9.1796875" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" customWidth="1"/>
+    <col min="9" max="9" width="15.36328125" customWidth="1"/>
+    <col min="10" max="10" width="12.81640625" customWidth="1"/>
+    <col min="11" max="11" width="22.54296875" customWidth="1"/>
+    <col min="12" max="12" width="9.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>12</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="F1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="F2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2" s="3">
+        <v>45017</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -1246,79 +1172,125 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2">
+    <cfRule type="containsText" dxfId="19" priority="1" operator="containsText" text="Dog ID">
+      <formula>NOT(ISERROR(SEARCH("Dog ID",A2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8">
+    <cfRule type="containsText" dxfId="18" priority="3" operator="containsText" text="Client ID">
+      <formula>NOT(ISERROR(SEARCH("Client ID",A8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2">
+    <cfRule type="containsText" dxfId="17" priority="2" operator="containsText" text="PK">
+      <formula>NOT(ISERROR(SEARCH("PK",B2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B8">
     <cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="FK">
       <formula>NOT(ISERROR(SEARCH("FK",B8)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A8">
-    <cfRule type="containsText" dxfId="15" priority="3" operator="containsText" text="Client ID">
-      <formula>NOT(ISERROR(SEARCH("Client ID",A8)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2">
-    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="PK">
-      <formula>NOT(ISERROR(SEARCH("PK",B2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2">
-    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="Dog ID">
-      <formula>NOT(ISERROR(SEARCH("Dog ID",A2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46288B5F-40C9-4A86-89BA-7773ED747D88}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.36328125" customWidth="1"/>
     <col min="2" max="2" width="19.26953125" customWidth="1"/>
+    <col min="4" max="4" width="16.453125" customWidth="1"/>
+    <col min="5" max="5" width="14.7265625" customWidth="1"/>
+    <col min="7" max="7" width="15.453125" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="9.7265625" customWidth="1"/>
+    <col min="10" max="10" width="10.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>20</v>
       </c>
       <c r="B1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="D2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3">
+        <v>46130</v>
+      </c>
+      <c r="F2" s="6">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="G2" s="5">
+        <v>3.142361111111111E-2</v>
+      </c>
+      <c r="H2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -1327,79 +1299,126 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2">
+    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="Appointment ID">
+      <formula>NOT(ISERROR(SEARCH("Appointment ID",A2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7">
+    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="Client ID">
+      <formula>NOT(ISERROR(SEARCH("Client ID",A7)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:B2">
+    <cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="PK">
+      <formula>NOT(ISERROR(SEARCH("PK",A2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="containsText" dxfId="26" priority="4" operator="containsText" text="FK">
+    <cfRule type="containsText" dxfId="12" priority="4" operator="containsText" text="FK">
       <formula>NOT(ISERROR(SEARCH("FK",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7">
-    <cfRule type="containsText" dxfId="25" priority="3" operator="containsText" text="Client ID">
-      <formula>NOT(ISERROR(SEARCH("Client ID",A7)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B2">
-    <cfRule type="containsText" dxfId="24" priority="2" operator="containsText" text="PK">
-      <formula>NOT(ISERROR(SEARCH("PK",A2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2">
-    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="Appointment ID">
-      <formula>NOT(ISERROR(SEARCH("Appointment ID",A2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{684FE32D-145A-47FD-B6AB-AE96F5ABA92D}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.81640625" customWidth="1"/>
     <col min="2" max="2" width="19.453125" customWidth="1"/>
+    <col min="4" max="4" width="12.453125" customWidth="1"/>
+    <col min="5" max="5" width="25.81640625" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" customWidth="1"/>
+    <col min="7" max="7" width="13.453125" customWidth="1"/>
+    <col min="8" max="8" width="12.81640625" customWidth="1"/>
+    <col min="9" max="9" width="15.26953125" customWidth="1"/>
+    <col min="10" max="10" width="11.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>26</v>
       </c>
       <c r="B1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>27</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="D2">
+        <v>10899</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1407,7 +1426,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1416,131 +1435,171 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A7:A8">
+    <cfRule type="containsText" dxfId="11" priority="4" operator="containsText" text="Appointment ID">
+      <formula>NOT(ISERROR(SEARCH("Appointment ID",A7)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8">
+    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="Dog ID">
+      <formula>NOT(ISERROR(SEARCH("Dog ID",A8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:B2">
+    <cfRule type="containsText" dxfId="9" priority="2" operator="containsText" text="Log ID">
+      <formula>NOT(ISERROR(SEARCH("Log ID",A2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2">
+    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="PK">
+      <formula>NOT(ISERROR(SEARCH("PK",B2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B7:B8">
-    <cfRule type="containsText" dxfId="38" priority="5" operator="containsText" text="FK">
+    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="FK">
       <formula>NOT(ISERROR(SEARCH("FK",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:A8">
-    <cfRule type="containsText" dxfId="37" priority="4" operator="containsText" text="Appointment ID">
-      <formula>NOT(ISERROR(SEARCH("Appointment ID",A7)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A8">
-    <cfRule type="containsText" dxfId="36" priority="3" operator="containsText" text="Dog ID">
-      <formula>NOT(ISERROR(SEARCH("Dog ID",A8)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B2">
-    <cfRule type="containsText" dxfId="35" priority="2" operator="containsText" text="Log ID">
-      <formula>NOT(ISERROR(SEARCH("Log ID",A2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2">
-    <cfRule type="containsText" dxfId="30" priority="1" operator="containsText" text="PK">
-      <formula>NOT(ISERROR(SEARCH("PK",B2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50392009-1A47-4584-9EDC-F724BB689B92}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.453125" customWidth="1"/>
     <col min="2" max="2" width="19.08984375" customWidth="1"/>
+    <col min="5" max="5" width="13.90625" customWidth="1"/>
+    <col min="6" max="6" width="16.36328125" customWidth="1"/>
+    <col min="7" max="7" width="22.453125" customWidth="1"/>
+    <col min="8" max="8" width="14.54296875" customWidth="1"/>
+    <col min="9" max="9" width="24.26953125" customWidth="1"/>
+    <col min="10" max="10" width="17.08984375" customWidth="1"/>
+    <col min="11" max="11" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>31</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="E1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>32</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="E2">
+        <v>24</v>
+      </c>
+      <c r="F2" s="3">
+        <v>46129</v>
+      </c>
+      <c r="G2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2">
+        <v>70</v>
+      </c>
+      <c r="I2">
+        <v>2387688</v>
+      </c>
+      <c r="J2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B7" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Payment ID">
+      <formula>NOT(ISERROR(SEARCH("Payment ID",A2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7">
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="Appointment ID">
+      <formula>NOT(ISERROR(SEARCH("Appointment ID",A7)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7:B7">
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="Appointment ID">
+      <formula>NOT(ISERROR(SEARCH("Appointment ID",A7)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="containsText" dxfId="57" priority="7" operator="containsText" text="PK">
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="PK">
       <formula>NOT(ISERROR(SEARCH("PK",B2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="2" operator="containsText" text="PK">
+    <cfRule type="containsText" dxfId="2" priority="7" operator="containsText" text="PK">
       <formula>NOT(ISERROR(SEARCH("PK",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A8:B8">
-    <cfRule type="containsText" dxfId="55" priority="6" operator="containsText" text="Appointment ID">
-      <formula>NOT(ISERROR(SEARCH("Appointment ID",A8)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
-    <cfRule type="containsText" dxfId="54" priority="5" operator="containsText" text="FK">
-      <formula>NOT(ISERROR(SEARCH("FK",B8)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="53" priority="4" operator="containsText" text="FK">
-      <formula>NOT(ISERROR(SEARCH("FK",B8)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A8">
-    <cfRule type="containsText" dxfId="52" priority="3" operator="containsText" text="Appointment ID">
-      <formula>NOT(ISERROR(SEARCH("Appointment ID",A8)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2">
-    <cfRule type="containsText" dxfId="45" priority="1" operator="containsText" text="Payment ID">
-      <formula>NOT(ISERROR(SEARCH("Payment ID",A2)))</formula>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="FK">
+      <formula>NOT(ISERROR(SEARCH("FK",B7)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="FK">
+      <formula>NOT(ISERROR(SEARCH("FK",B7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>